--- a/csv/policies/reference/Ref_OBPS/formula_Ref_OBPS_MB.xlsx
+++ b/csv/policies/reference/Ref_OBPS/formula_Ref_OBPS_MB.xlsx
@@ -1,167 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CIMS\dev\cims-models\csv\policies\reference\Ref_OBPS\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0113E405-0922-498E-BE0B-D8C9523BE5F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FEC1FE46-8BE9-490A-8688-9F806224DAF6}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="35">
-  <si>
-    <t>&lt;-- Navigate by typing to search</t>
-  </si>
-  <si>
-    <t>Branch</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Region</t>
-  </si>
-  <si>
-    <t>Sector</t>
-  </si>
-  <si>
-    <t>Service</t>
-  </si>
-  <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>Parameter</t>
-  </si>
-  <si>
-    <t>Context</t>
-  </si>
-  <si>
-    <t>Sub_Context</t>
-  </si>
-  <si>
-    <t>Target</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>CIMS.CAN.MB.Natural Gas</t>
-  </si>
-  <si>
-    <t>MB</t>
-  </si>
-  <si>
-    <t>Natural Gas</t>
-  </si>
-  <si>
-    <t>Tax</t>
-  </si>
-  <si>
-    <t>CO2</t>
-  </si>
-  <si>
-    <t>Combustion</t>
-  </si>
-  <si>
-    <t>Govt of Canada</t>
-  </si>
-  <si>
-    <t>$/tCO2e</t>
-  </si>
-  <si>
-    <t>CIMS.CAN.MB.Petroleum Crude</t>
-  </si>
-  <si>
-    <t>Petroleum Crude</t>
-  </si>
-  <si>
-    <t>CIMS.CAN.MB.Mining</t>
-  </si>
-  <si>
-    <t>Mining</t>
-  </si>
-  <si>
-    <t>CIMS.CAN.MB.Light Industrial.Manufacturing.Food Tobacco and Beverage</t>
-  </si>
-  <si>
-    <t>Food Tobacco and Beverage</t>
-  </si>
-  <si>
-    <t>CIMS.CAN.MB.Light Industrial.Manufacturing.Transportation Equipment</t>
-  </si>
-  <si>
-    <t>Transportation Equipment</t>
-  </si>
-  <si>
-    <t>CIMS.CAN.MB.Electricity</t>
-  </si>
-  <si>
-    <t>Electricity</t>
-  </si>
-  <si>
-    <t>Process</t>
-  </si>
-  <si>
-    <t>CH4</t>
-  </si>
-  <si>
-    <t>N2O</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -180,30 +49,86 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
+<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook r:id="rId1">
     <sheetNames>
       <sheetName val="Control"/>
       <sheetName val="Macro"/>
@@ -601,1839 +526,2303 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62698509-EB28-4595-83B1-F35C4F83A958}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:X26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
-        <v>0</v>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>&lt;-- Navigate by typing to search</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" t="s">
-        <v>12</v>
-      </c>
-      <c r="M2">
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Sub_Context</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
         <v>2000</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>2005</v>
       </c>
-      <c r="O2">
+      <c r="O2" t="n">
         <v>2010</v>
       </c>
-      <c r="P2">
+      <c r="P2" t="n">
         <v>2015</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" t="n">
         <v>2020</v>
       </c>
-      <c r="R2">
+      <c r="R2" t="n">
         <v>2025</v>
       </c>
-      <c r="S2">
+      <c r="S2" t="n">
         <v>2030</v>
       </c>
-      <c r="T2">
+      <c r="T2" t="n">
         <v>2035</v>
       </c>
-      <c r="U2">
+      <c r="U2" t="n">
         <v>2040</v>
       </c>
-      <c r="V2">
+      <c r="V2" t="n">
         <v>2045</v>
       </c>
-      <c r="W2">
+      <c r="W2" t="n">
         <v>2050</v>
       </c>
-      <c r="X2" t="s">
-        <v>13</v>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" t="s">
-        <v>21</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.MB.Natural Gas</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Natural Gas</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CO2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Combustion</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Govt of Canada</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>$/tCO2e</t>
+        </is>
       </c>
       <c r="M3">
         <f>[1]Prices!K$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N3">
         <f>[1]Prices!L$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O3">
         <f>[1]Prices!M$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P3">
         <f>[1]Prices!N$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q3">
         <f>[1]Prices!O$26</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="R3">
         <f>[1]Prices!P$26</f>
-        <v>68.341643330825832</v>
+        <v/>
       </c>
       <c r="S3">
         <f>[1]Prices!Q$26</f>
-        <v>100.32134973994673</v>
+        <v/>
       </c>
       <c r="T3">
         <f>[1]Prices!R$26</f>
-        <v>82.639006798408047</v>
+        <v/>
       </c>
       <c r="U3">
         <f>[1]Prices!S$26</f>
-        <v>67.75892127087694</v>
+        <v/>
       </c>
       <c r="V3">
         <f>[1]Prices!T$26</f>
-        <v>55.57940835560332</v>
+        <v/>
       </c>
       <c r="W3">
         <f>[1]Prices!U$26</f>
-        <v>45.789061745779293</v>
+        <v/>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L4" t="s">
-        <v>21</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.MB.Petroleum Crude</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Petroleum Crude</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CO2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Combustion</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Govt of Canada</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>$/tCO2e</t>
+        </is>
       </c>
       <c r="M4">
         <f>[1]Prices!K$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N4">
         <f>[1]Prices!L$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O4">
         <f>[1]Prices!M$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P4">
         <f>[1]Prices!N$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q4">
         <f>[1]Prices!O$26</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="R4">
         <f>[1]Prices!P$26</f>
-        <v>68.341643330825832</v>
+        <v/>
       </c>
       <c r="S4">
         <f>[1]Prices!Q$26</f>
-        <v>100.32134973994673</v>
+        <v/>
       </c>
       <c r="T4">
         <f>[1]Prices!R$26</f>
-        <v>82.639006798408047</v>
+        <v/>
       </c>
       <c r="U4">
         <f>[1]Prices!S$26</f>
-        <v>67.75892127087694</v>
+        <v/>
       </c>
       <c r="V4">
         <f>[1]Prices!T$26</f>
-        <v>55.57940835560332</v>
+        <v/>
       </c>
       <c r="W4">
         <f>[1]Prices!U$26</f>
-        <v>45.789061745779293</v>
+        <v/>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" t="s">
-        <v>20</v>
-      </c>
-      <c r="L5" t="s">
-        <v>21</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.MB.Mining</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CO2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Combustion</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Govt of Canada</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>$/tCO2e</t>
+        </is>
       </c>
       <c r="M5">
         <f>[1]Prices!K$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N5">
         <f>[1]Prices!L$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O5">
         <f>[1]Prices!M$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P5">
         <f>[1]Prices!N$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q5">
         <f>[1]Prices!O$26</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="R5">
         <f>[1]Prices!P$26</f>
-        <v>68.341643330825832</v>
+        <v/>
       </c>
       <c r="S5">
         <f>[1]Prices!Q$26</f>
-        <v>100.32134973994673</v>
+        <v/>
       </c>
       <c r="T5">
         <f>[1]Prices!R$26</f>
-        <v>82.639006798408047</v>
+        <v/>
       </c>
       <c r="U5">
         <f>[1]Prices!S$26</f>
-        <v>67.75892127087694</v>
+        <v/>
       </c>
       <c r="V5">
         <f>[1]Prices!T$26</f>
-        <v>55.57940835560332</v>
+        <v/>
       </c>
       <c r="W5">
         <f>[1]Prices!U$26</f>
-        <v>45.789061745779293</v>
+        <v/>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6" t="s">
-        <v>20</v>
-      </c>
-      <c r="L6" t="s">
-        <v>21</v>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.MB.Light Industrial.Manufacturing.Food Tobacco and Beverage</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Food Tobacco and Beverage</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CO2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Combustion</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Govt of Canada</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>$/tCO2e</t>
+        </is>
       </c>
       <c r="M6">
         <f>[1]Prices!K$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N6">
         <f>[1]Prices!L$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O6">
         <f>[1]Prices!M$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P6">
         <f>[1]Prices!N$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q6">
         <f>[1]Prices!O$26</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="R6">
         <f>[1]Prices!P$26</f>
-        <v>68.341643330825832</v>
+        <v/>
       </c>
       <c r="S6">
         <f>[1]Prices!Q$26</f>
-        <v>100.32134973994673</v>
+        <v/>
       </c>
       <c r="T6">
         <f>[1]Prices!R$26</f>
-        <v>82.639006798408047</v>
+        <v/>
       </c>
       <c r="U6">
         <f>[1]Prices!S$26</f>
-        <v>67.75892127087694</v>
+        <v/>
       </c>
       <c r="V6">
         <f>[1]Prices!T$26</f>
-        <v>55.57940835560332</v>
+        <v/>
       </c>
       <c r="W6">
         <f>[1]Prices!U$26</f>
-        <v>45.789061745779293</v>
+        <v/>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K7" t="s">
-        <v>20</v>
-      </c>
-      <c r="L7" t="s">
-        <v>21</v>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.MB.Light Industrial.Manufacturing.Transportation Equipment</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Transportation Equipment</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>CO2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Combustion</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Govt of Canada</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>$/tCO2e</t>
+        </is>
       </c>
       <c r="M7">
         <f>[1]Prices!K$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N7">
         <f>[1]Prices!L$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O7">
         <f>[1]Prices!M$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P7">
         <f>[1]Prices!N$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q7">
         <f>[1]Prices!O$26</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="R7">
         <f>[1]Prices!P$26</f>
-        <v>68.341643330825832</v>
+        <v/>
       </c>
       <c r="S7">
         <f>[1]Prices!Q$26</f>
-        <v>100.32134973994673</v>
+        <v/>
       </c>
       <c r="T7">
         <f>[1]Prices!R$26</f>
-        <v>82.639006798408047</v>
+        <v/>
       </c>
       <c r="U7">
         <f>[1]Prices!S$26</f>
-        <v>67.75892127087694</v>
+        <v/>
       </c>
       <c r="V7">
         <f>[1]Prices!T$26</f>
-        <v>55.57940835560332</v>
+        <v/>
       </c>
       <c r="W7">
         <f>[1]Prices!U$26</f>
-        <v>45.789061745779293</v>
+        <v/>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" t="s">
-        <v>19</v>
-      </c>
-      <c r="K8" t="s">
-        <v>20</v>
-      </c>
-      <c r="L8" t="s">
-        <v>21</v>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.MB.Electricity</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>CO2</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Combustion</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Govt of Canada</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>$/tCO2e</t>
+        </is>
       </c>
       <c r="M8">
         <f>[1]Prices!K$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N8">
         <f>[1]Prices!L$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O8">
         <f>[1]Prices!M$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P8">
         <f>[1]Prices!N$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q8">
         <f>[1]Prices!O$26</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="R8">
         <f>[1]Prices!P$26</f>
-        <v>68.341643330825832</v>
+        <v/>
       </c>
       <c r="S8">
         <f>[1]Prices!Q$26</f>
-        <v>100.32134973994673</v>
+        <v/>
       </c>
       <c r="T8">
         <f>[1]Prices!R$26</f>
-        <v>82.639006798408047</v>
+        <v/>
       </c>
       <c r="U8">
         <f>[1]Prices!S$26</f>
-        <v>67.75892127087694</v>
+        <v/>
       </c>
       <c r="V8">
         <f>[1]Prices!T$26</f>
-        <v>55.57940835560332</v>
+        <v/>
       </c>
       <c r="W8">
         <f>[1]Prices!U$26</f>
-        <v>45.789061745779293</v>
+        <v/>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" t="s">
-        <v>32</v>
-      </c>
-      <c r="K9" t="s">
-        <v>20</v>
-      </c>
-      <c r="L9" t="s">
-        <v>21</v>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.MB.Natural Gas</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Natural Gas</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>CO2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Govt of Canada</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>$/tCO2e</t>
+        </is>
       </c>
       <c r="M9">
         <f>[1]Prices!K$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N9">
         <f>[1]Prices!L$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O9">
         <f>[1]Prices!M$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P9">
         <f>[1]Prices!N$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q9">
         <f>[1]Prices!O$26</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="R9">
         <f>[1]Prices!P$26</f>
-        <v>68.341643330825832</v>
+        <v/>
       </c>
       <c r="S9">
         <f>[1]Prices!Q$26</f>
-        <v>100.32134973994673</v>
+        <v/>
       </c>
       <c r="T9">
         <f>[1]Prices!R$26</f>
-        <v>82.639006798408047</v>
+        <v/>
       </c>
       <c r="U9">
         <f>[1]Prices!S$26</f>
-        <v>67.75892127087694</v>
+        <v/>
       </c>
       <c r="V9">
         <f>[1]Prices!T$26</f>
-        <v>55.57940835560332</v>
+        <v/>
       </c>
       <c r="W9">
         <f>[1]Prices!U$26</f>
-        <v>45.789061745779293</v>
+        <v/>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10" t="s">
-        <v>18</v>
-      </c>
-      <c r="I10" t="s">
-        <v>32</v>
-      </c>
-      <c r="K10" t="s">
-        <v>20</v>
-      </c>
-      <c r="L10" t="s">
-        <v>21</v>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.MB.Petroleum Crude</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Petroleum Crude</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>CO2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Govt of Canada</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>$/tCO2e</t>
+        </is>
       </c>
       <c r="M10">
         <f>[1]Prices!K$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N10">
         <f>[1]Prices!L$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O10">
         <f>[1]Prices!M$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P10">
         <f>[1]Prices!N$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q10">
         <f>[1]Prices!O$26</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="R10">
         <f>[1]Prices!P$26</f>
-        <v>68.341643330825832</v>
+        <v/>
       </c>
       <c r="S10">
         <f>[1]Prices!Q$26</f>
-        <v>100.32134973994673</v>
+        <v/>
       </c>
       <c r="T10">
         <f>[1]Prices!R$26</f>
-        <v>82.639006798408047</v>
+        <v/>
       </c>
       <c r="U10">
         <f>[1]Prices!S$26</f>
-        <v>67.75892127087694</v>
+        <v/>
       </c>
       <c r="V10">
         <f>[1]Prices!T$26</f>
-        <v>55.57940835560332</v>
+        <v/>
       </c>
       <c r="W10">
         <f>[1]Prices!U$26</f>
-        <v>45.789061745779293</v>
+        <v/>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" t="s">
-        <v>32</v>
-      </c>
-      <c r="K11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L11" t="s">
-        <v>21</v>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.MB.Mining</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>CO2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Govt of Canada</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>$/tCO2e</t>
+        </is>
       </c>
       <c r="M11">
         <f>[1]Prices!K$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N11">
         <f>[1]Prices!L$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O11">
         <f>[1]Prices!M$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P11">
         <f>[1]Prices!N$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q11">
         <f>[1]Prices!O$26</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="R11">
         <f>[1]Prices!P$26</f>
-        <v>68.341643330825832</v>
+        <v/>
       </c>
       <c r="S11">
         <f>[1]Prices!Q$26</f>
-        <v>100.32134973994673</v>
+        <v/>
       </c>
       <c r="T11">
         <f>[1]Prices!R$26</f>
-        <v>82.639006798408047</v>
+        <v/>
       </c>
       <c r="U11">
         <f>[1]Prices!S$26</f>
-        <v>67.75892127087694</v>
+        <v/>
       </c>
       <c r="V11">
         <f>[1]Prices!T$26</f>
-        <v>55.57940835560332</v>
+        <v/>
       </c>
       <c r="W11">
         <f>[1]Prices!U$26</f>
-        <v>45.789061745779293</v>
+        <v/>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" t="s">
-        <v>18</v>
-      </c>
-      <c r="I12" t="s">
-        <v>32</v>
-      </c>
-      <c r="K12" t="s">
-        <v>20</v>
-      </c>
-      <c r="L12" t="s">
-        <v>21</v>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.MB.Light Industrial.Manufacturing.Food Tobacco and Beverage</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Food Tobacco and Beverage</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>CO2</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Govt of Canada</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>$/tCO2e</t>
+        </is>
       </c>
       <c r="M12">
         <f>[1]Prices!K$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N12">
         <f>[1]Prices!L$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O12">
         <f>[1]Prices!M$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P12">
         <f>[1]Prices!N$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q12">
         <f>[1]Prices!O$26</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="R12">
         <f>[1]Prices!P$26</f>
-        <v>68.341643330825832</v>
+        <v/>
       </c>
       <c r="S12">
         <f>[1]Prices!Q$26</f>
-        <v>100.32134973994673</v>
+        <v/>
       </c>
       <c r="T12">
         <f>[1]Prices!R$26</f>
-        <v>82.639006798408047</v>
+        <v/>
       </c>
       <c r="U12">
         <f>[1]Prices!S$26</f>
-        <v>67.75892127087694</v>
+        <v/>
       </c>
       <c r="V12">
         <f>[1]Prices!T$26</f>
-        <v>55.57940835560332</v>
+        <v/>
       </c>
       <c r="W12">
         <f>[1]Prices!U$26</f>
-        <v>45.789061745779293</v>
+        <v/>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" t="s">
-        <v>29</v>
-      </c>
-      <c r="G13" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13" t="s">
-        <v>18</v>
-      </c>
-      <c r="I13" t="s">
-        <v>32</v>
-      </c>
-      <c r="K13" t="s">
-        <v>20</v>
-      </c>
-      <c r="L13" t="s">
-        <v>21</v>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.MB.Light Industrial.Manufacturing.Transportation Equipment</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Transportation Equipment</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>CO2</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Govt of Canada</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>$/tCO2e</t>
+        </is>
       </c>
       <c r="M13">
         <f>[1]Prices!K$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N13">
         <f>[1]Prices!L$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O13">
         <f>[1]Prices!M$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P13">
         <f>[1]Prices!N$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q13">
         <f>[1]Prices!O$26</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="R13">
         <f>[1]Prices!P$26</f>
-        <v>68.341643330825832</v>
+        <v/>
       </c>
       <c r="S13">
         <f>[1]Prices!Q$26</f>
-        <v>100.32134973994673</v>
+        <v/>
       </c>
       <c r="T13">
         <f>[1]Prices!R$26</f>
-        <v>82.639006798408047</v>
+        <v/>
       </c>
       <c r="U13">
         <f>[1]Prices!S$26</f>
-        <v>67.75892127087694</v>
+        <v/>
       </c>
       <c r="V13">
         <f>[1]Prices!T$26</f>
-        <v>55.57940835560332</v>
+        <v/>
       </c>
       <c r="W13">
         <f>[1]Prices!U$26</f>
-        <v>45.789061745779293</v>
+        <v/>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" t="s">
-        <v>18</v>
-      </c>
-      <c r="I14" t="s">
-        <v>32</v>
-      </c>
-      <c r="K14" t="s">
-        <v>20</v>
-      </c>
-      <c r="L14" t="s">
-        <v>21</v>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.MB.Electricity</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>CO2</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Govt of Canada</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>$/tCO2e</t>
+        </is>
       </c>
       <c r="M14">
         <f>[1]Prices!K$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N14">
         <f>[1]Prices!L$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O14">
         <f>[1]Prices!M$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P14">
         <f>[1]Prices!N$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q14">
         <f>[1]Prices!O$26</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="R14">
         <f>[1]Prices!P$26</f>
-        <v>68.341643330825832</v>
+        <v/>
       </c>
       <c r="S14">
         <f>[1]Prices!Q$26</f>
-        <v>100.32134973994673</v>
+        <v/>
       </c>
       <c r="T14">
         <f>[1]Prices!R$26</f>
-        <v>82.639006798408047</v>
+        <v/>
       </c>
       <c r="U14">
         <f>[1]Prices!S$26</f>
-        <v>67.75892127087694</v>
+        <v/>
       </c>
       <c r="V14">
         <f>[1]Prices!T$26</f>
-        <v>55.57940835560332</v>
+        <v/>
       </c>
       <c r="W14">
         <f>[1]Prices!U$26</f>
-        <v>45.789061745779293</v>
+        <v/>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15" t="s">
-        <v>33</v>
-      </c>
-      <c r="I15" t="s">
-        <v>32</v>
-      </c>
-      <c r="K15" t="s">
-        <v>20</v>
-      </c>
-      <c r="L15" t="s">
-        <v>21</v>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.MB.Natural Gas</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Natural Gas</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Govt of Canada</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>$/tCO2e</t>
+        </is>
       </c>
       <c r="M15">
         <f>[1]Prices!K$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N15">
         <f>[1]Prices!L$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O15">
         <f>[1]Prices!M$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P15">
         <f>[1]Prices!N$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q15">
         <f>[1]Prices!O$26</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="R15">
         <f>[1]Prices!P$26</f>
-        <v>68.341643330825832</v>
+        <v/>
       </c>
       <c r="S15">
         <f>[1]Prices!Q$26</f>
-        <v>100.32134973994673</v>
+        <v/>
       </c>
       <c r="T15">
         <f>[1]Prices!R$26</f>
-        <v>82.639006798408047</v>
+        <v/>
       </c>
       <c r="U15">
         <f>[1]Prices!S$26</f>
-        <v>67.75892127087694</v>
+        <v/>
       </c>
       <c r="V15">
         <f>[1]Prices!T$26</f>
-        <v>55.57940835560332</v>
+        <v/>
       </c>
       <c r="W15">
         <f>[1]Prices!U$26</f>
-        <v>45.789061745779293</v>
+        <v/>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" t="s">
-        <v>17</v>
-      </c>
-      <c r="H16" t="s">
-        <v>33</v>
-      </c>
-      <c r="I16" t="s">
-        <v>32</v>
-      </c>
-      <c r="K16" t="s">
-        <v>20</v>
-      </c>
-      <c r="L16" t="s">
-        <v>21</v>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.MB.Petroleum Crude</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Petroleum Crude</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Govt of Canada</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>$/tCO2e</t>
+        </is>
       </c>
       <c r="M16">
         <f>[1]Prices!K$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N16">
         <f>[1]Prices!L$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O16">
         <f>[1]Prices!M$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P16">
         <f>[1]Prices!N$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q16">
         <f>[1]Prices!O$26</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="R16">
         <f>[1]Prices!P$26</f>
-        <v>68.341643330825832</v>
+        <v/>
       </c>
       <c r="S16">
         <f>[1]Prices!Q$26</f>
-        <v>100.32134973994673</v>
+        <v/>
       </c>
       <c r="T16">
         <f>[1]Prices!R$26</f>
-        <v>82.639006798408047</v>
+        <v/>
       </c>
       <c r="U16">
         <f>[1]Prices!S$26</f>
-        <v>67.75892127087694</v>
+        <v/>
       </c>
       <c r="V16">
         <f>[1]Prices!T$26</f>
-        <v>55.57940835560332</v>
+        <v/>
       </c>
       <c r="W16">
         <f>[1]Prices!U$26</f>
-        <v>45.789061745779293</v>
+        <v/>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" t="s">
-        <v>17</v>
-      </c>
-      <c r="H17" t="s">
-        <v>33</v>
-      </c>
-      <c r="I17" t="s">
-        <v>32</v>
-      </c>
-      <c r="K17" t="s">
-        <v>20</v>
-      </c>
-      <c r="L17" t="s">
-        <v>21</v>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.MB.Mining</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Govt of Canada</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>$/tCO2e</t>
+        </is>
       </c>
       <c r="M17">
         <f>[1]Prices!K$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N17">
         <f>[1]Prices!L$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O17">
         <f>[1]Prices!M$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P17">
         <f>[1]Prices!N$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q17">
         <f>[1]Prices!O$26</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="R17">
         <f>[1]Prices!P$26</f>
-        <v>68.341643330825832</v>
+        <v/>
       </c>
       <c r="S17">
         <f>[1]Prices!Q$26</f>
-        <v>100.32134973994673</v>
+        <v/>
       </c>
       <c r="T17">
         <f>[1]Prices!R$26</f>
-        <v>82.639006798408047</v>
+        <v/>
       </c>
       <c r="U17">
         <f>[1]Prices!S$26</f>
-        <v>67.75892127087694</v>
+        <v/>
       </c>
       <c r="V17">
         <f>[1]Prices!T$26</f>
-        <v>55.57940835560332</v>
+        <v/>
       </c>
       <c r="W17">
         <f>[1]Prices!U$26</f>
-        <v>45.789061745779293</v>
+        <v/>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" t="s">
-        <v>27</v>
-      </c>
-      <c r="G18" t="s">
-        <v>17</v>
-      </c>
-      <c r="H18" t="s">
-        <v>33</v>
-      </c>
-      <c r="I18" t="s">
-        <v>32</v>
-      </c>
-      <c r="K18" t="s">
-        <v>20</v>
-      </c>
-      <c r="L18" t="s">
-        <v>21</v>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.MB.Light Industrial.Manufacturing.Food Tobacco and Beverage</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Food Tobacco and Beverage</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Govt of Canada</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>$/tCO2e</t>
+        </is>
       </c>
       <c r="M18">
         <f>[1]Prices!K$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N18">
         <f>[1]Prices!L$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O18">
         <f>[1]Prices!M$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P18">
         <f>[1]Prices!N$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q18">
         <f>[1]Prices!O$26</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="R18">
         <f>[1]Prices!P$26</f>
-        <v>68.341643330825832</v>
+        <v/>
       </c>
       <c r="S18">
         <f>[1]Prices!Q$26</f>
-        <v>100.32134973994673</v>
+        <v/>
       </c>
       <c r="T18">
         <f>[1]Prices!R$26</f>
-        <v>82.639006798408047</v>
+        <v/>
       </c>
       <c r="U18">
         <f>[1]Prices!S$26</f>
-        <v>67.75892127087694</v>
+        <v/>
       </c>
       <c r="V18">
         <f>[1]Prices!T$26</f>
-        <v>55.57940835560332</v>
+        <v/>
       </c>
       <c r="W18">
         <f>[1]Prices!U$26</f>
-        <v>45.789061745779293</v>
+        <v/>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" t="s">
-        <v>4</v>
-      </c>
-      <c r="C19" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" t="s">
-        <v>29</v>
-      </c>
-      <c r="G19" t="s">
-        <v>17</v>
-      </c>
-      <c r="H19" t="s">
-        <v>33</v>
-      </c>
-      <c r="I19" t="s">
-        <v>32</v>
-      </c>
-      <c r="K19" t="s">
-        <v>20</v>
-      </c>
-      <c r="L19" t="s">
-        <v>21</v>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.MB.Light Industrial.Manufacturing.Transportation Equipment</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Transportation Equipment</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Govt of Canada</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>$/tCO2e</t>
+        </is>
       </c>
       <c r="M19">
         <f>[1]Prices!K$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N19">
         <f>[1]Prices!L$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O19">
         <f>[1]Prices!M$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P19">
         <f>[1]Prices!N$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q19">
         <f>[1]Prices!O$26</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="R19">
         <f>[1]Prices!P$26</f>
-        <v>68.341643330825832</v>
+        <v/>
       </c>
       <c r="S19">
         <f>[1]Prices!Q$26</f>
-        <v>100.32134973994673</v>
+        <v/>
       </c>
       <c r="T19">
         <f>[1]Prices!R$26</f>
-        <v>82.639006798408047</v>
+        <v/>
       </c>
       <c r="U19">
         <f>[1]Prices!S$26</f>
-        <v>67.75892127087694</v>
+        <v/>
       </c>
       <c r="V19">
         <f>[1]Prices!T$26</f>
-        <v>55.57940835560332</v>
+        <v/>
       </c>
       <c r="W19">
         <f>[1]Prices!U$26</f>
-        <v>45.789061745779293</v>
+        <v/>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" t="s">
-        <v>31</v>
-      </c>
-      <c r="G20" t="s">
-        <v>17</v>
-      </c>
-      <c r="H20" t="s">
-        <v>33</v>
-      </c>
-      <c r="I20" t="s">
-        <v>32</v>
-      </c>
-      <c r="K20" t="s">
-        <v>20</v>
-      </c>
-      <c r="L20" t="s">
-        <v>21</v>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.MB.Electricity</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>CH4</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Govt of Canada</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>$/tCO2e</t>
+        </is>
       </c>
       <c r="M20">
         <f>[1]Prices!K$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N20">
         <f>[1]Prices!L$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O20">
         <f>[1]Prices!M$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P20">
         <f>[1]Prices!N$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q20">
         <f>[1]Prices!O$26</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="R20">
         <f>[1]Prices!P$26</f>
-        <v>68.341643330825832</v>
+        <v/>
       </c>
       <c r="S20">
         <f>[1]Prices!Q$26</f>
-        <v>100.32134973994673</v>
+        <v/>
       </c>
       <c r="T20">
         <f>[1]Prices!R$26</f>
-        <v>82.639006798408047</v>
+        <v/>
       </c>
       <c r="U20">
         <f>[1]Prices!S$26</f>
-        <v>67.75892127087694</v>
+        <v/>
       </c>
       <c r="V20">
         <f>[1]Prices!T$26</f>
-        <v>55.57940835560332</v>
+        <v/>
       </c>
       <c r="W20">
         <f>[1]Prices!U$26</f>
-        <v>45.789061745779293</v>
+        <v/>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" t="s">
-        <v>16</v>
-      </c>
-      <c r="G21" t="s">
-        <v>17</v>
-      </c>
-      <c r="H21" t="s">
-        <v>34</v>
-      </c>
-      <c r="I21" t="s">
-        <v>32</v>
-      </c>
-      <c r="K21" t="s">
-        <v>20</v>
-      </c>
-      <c r="L21" t="s">
-        <v>21</v>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.MB.Natural Gas</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Natural Gas</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>N2O</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Govt of Canada</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>$/tCO2e</t>
+        </is>
       </c>
       <c r="M21">
         <f>[1]Prices!K$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N21">
         <f>[1]Prices!L$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O21">
         <f>[1]Prices!M$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P21">
         <f>[1]Prices!N$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q21">
         <f>[1]Prices!O$26</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="R21">
         <f>[1]Prices!P$26</f>
-        <v>68.341643330825832</v>
+        <v/>
       </c>
       <c r="S21">
         <f>[1]Prices!Q$26</f>
-        <v>100.32134973994673</v>
+        <v/>
       </c>
       <c r="T21">
         <f>[1]Prices!R$26</f>
-        <v>82.639006798408047</v>
+        <v/>
       </c>
       <c r="U21">
         <f>[1]Prices!S$26</f>
-        <v>67.75892127087694</v>
+        <v/>
       </c>
       <c r="V21">
         <f>[1]Prices!T$26</f>
-        <v>55.57940835560332</v>
+        <v/>
       </c>
       <c r="W21">
         <f>[1]Prices!U$26</f>
-        <v>45.789061745779293</v>
+        <v/>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" t="s">
-        <v>15</v>
-      </c>
-      <c r="D22" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" t="s">
-        <v>17</v>
-      </c>
-      <c r="H22" t="s">
-        <v>34</v>
-      </c>
-      <c r="I22" t="s">
-        <v>32</v>
-      </c>
-      <c r="K22" t="s">
-        <v>20</v>
-      </c>
-      <c r="L22" t="s">
-        <v>21</v>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.MB.Petroleum Crude</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Petroleum Crude</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>N2O</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Govt of Canada</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>$/tCO2e</t>
+        </is>
       </c>
       <c r="M22">
         <f>[1]Prices!K$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N22">
         <f>[1]Prices!L$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O22">
         <f>[1]Prices!M$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P22">
         <f>[1]Prices!N$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q22">
         <f>[1]Prices!O$26</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="R22">
         <f>[1]Prices!P$26</f>
-        <v>68.341643330825832</v>
+        <v/>
       </c>
       <c r="S22">
         <f>[1]Prices!Q$26</f>
-        <v>100.32134973994673</v>
+        <v/>
       </c>
       <c r="T22">
         <f>[1]Prices!R$26</f>
-        <v>82.639006798408047</v>
+        <v/>
       </c>
       <c r="U22">
         <f>[1]Prices!S$26</f>
-        <v>67.75892127087694</v>
+        <v/>
       </c>
       <c r="V22">
         <f>[1]Prices!T$26</f>
-        <v>55.57940835560332</v>
+        <v/>
       </c>
       <c r="W22">
         <f>[1]Prices!U$26</f>
-        <v>45.789061745779293</v>
+        <v/>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" t="s">
-        <v>25</v>
-      </c>
-      <c r="G23" t="s">
-        <v>17</v>
-      </c>
-      <c r="H23" t="s">
-        <v>34</v>
-      </c>
-      <c r="I23" t="s">
-        <v>32</v>
-      </c>
-      <c r="K23" t="s">
-        <v>20</v>
-      </c>
-      <c r="L23" t="s">
-        <v>21</v>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.MB.Mining</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>N2O</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Govt of Canada</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>$/tCO2e</t>
+        </is>
       </c>
       <c r="M23">
         <f>[1]Prices!K$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N23">
         <f>[1]Prices!L$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O23">
         <f>[1]Prices!M$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P23">
         <f>[1]Prices!N$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q23">
         <f>[1]Prices!O$26</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="R23">
         <f>[1]Prices!P$26</f>
-        <v>68.341643330825832</v>
+        <v/>
       </c>
       <c r="S23">
         <f>[1]Prices!Q$26</f>
-        <v>100.32134973994673</v>
+        <v/>
       </c>
       <c r="T23">
         <f>[1]Prices!R$26</f>
-        <v>82.639006798408047</v>
+        <v/>
       </c>
       <c r="U23">
         <f>[1]Prices!S$26</f>
-        <v>67.75892127087694</v>
+        <v/>
       </c>
       <c r="V23">
         <f>[1]Prices!T$26</f>
-        <v>55.57940835560332</v>
+        <v/>
       </c>
       <c r="W23">
         <f>[1]Prices!U$26</f>
-        <v>45.789061745779293</v>
+        <v/>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" t="s">
-        <v>27</v>
-      </c>
-      <c r="G24" t="s">
-        <v>17</v>
-      </c>
-      <c r="H24" t="s">
-        <v>34</v>
-      </c>
-      <c r="I24" t="s">
-        <v>32</v>
-      </c>
-      <c r="K24" t="s">
-        <v>20</v>
-      </c>
-      <c r="L24" t="s">
-        <v>21</v>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.MB.Light Industrial.Manufacturing.Food Tobacco and Beverage</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Food Tobacco and Beverage</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>N2O</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Govt of Canada</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>$/tCO2e</t>
+        </is>
       </c>
       <c r="M24">
         <f>[1]Prices!K$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N24">
         <f>[1]Prices!L$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O24">
         <f>[1]Prices!M$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P24">
         <f>[1]Prices!N$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q24">
         <f>[1]Prices!O$26</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="R24">
         <f>[1]Prices!P$26</f>
-        <v>68.341643330825832</v>
+        <v/>
       </c>
       <c r="S24">
         <f>[1]Prices!Q$26</f>
-        <v>100.32134973994673</v>
+        <v/>
       </c>
       <c r="T24">
         <f>[1]Prices!R$26</f>
-        <v>82.639006798408047</v>
+        <v/>
       </c>
       <c r="U24">
         <f>[1]Prices!S$26</f>
-        <v>67.75892127087694</v>
+        <v/>
       </c>
       <c r="V24">
         <f>[1]Prices!T$26</f>
-        <v>55.57940835560332</v>
+        <v/>
       </c>
       <c r="W24">
         <f>[1]Prices!U$26</f>
-        <v>45.789061745779293</v>
+        <v/>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>28</v>
-      </c>
-      <c r="B25" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" t="s">
-        <v>29</v>
-      </c>
-      <c r="G25" t="s">
-        <v>17</v>
-      </c>
-      <c r="H25" t="s">
-        <v>34</v>
-      </c>
-      <c r="I25" t="s">
-        <v>32</v>
-      </c>
-      <c r="K25" t="s">
-        <v>20</v>
-      </c>
-      <c r="L25" t="s">
-        <v>21</v>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.MB.Light Industrial.Manufacturing.Transportation Equipment</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Transportation Equipment</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>N2O</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Govt of Canada</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>$/tCO2e</t>
+        </is>
       </c>
       <c r="M25">
         <f>[1]Prices!K$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N25">
         <f>[1]Prices!L$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O25">
         <f>[1]Prices!M$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P25">
         <f>[1]Prices!N$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q25">
         <f>[1]Prices!O$26</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="R25">
         <f>[1]Prices!P$26</f>
-        <v>68.341643330825832</v>
+        <v/>
       </c>
       <c r="S25">
         <f>[1]Prices!Q$26</f>
-        <v>100.32134973994673</v>
+        <v/>
       </c>
       <c r="T25">
         <f>[1]Prices!R$26</f>
-        <v>82.639006798408047</v>
+        <v/>
       </c>
       <c r="U25">
         <f>[1]Prices!S$26</f>
-        <v>67.75892127087694</v>
+        <v/>
       </c>
       <c r="V25">
         <f>[1]Prices!T$26</f>
-        <v>55.57940835560332</v>
+        <v/>
       </c>
       <c r="W25">
         <f>[1]Prices!U$26</f>
-        <v>45.789061745779293</v>
+        <v/>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" t="s">
-        <v>4</v>
-      </c>
-      <c r="C26" t="s">
-        <v>15</v>
-      </c>
-      <c r="D26" t="s">
-        <v>31</v>
-      </c>
-      <c r="G26" t="s">
-        <v>17</v>
-      </c>
-      <c r="H26" t="s">
-        <v>34</v>
-      </c>
-      <c r="I26" t="s">
-        <v>32</v>
-      </c>
-      <c r="K26" t="s">
-        <v>20</v>
-      </c>
-      <c r="L26" t="s">
-        <v>21</v>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CIMS.CAN.MB.Electricity</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>N2O</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Govt of Canada</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>$/tCO2e</t>
+        </is>
       </c>
       <c r="M26">
         <f>[1]Prices!K$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="N26">
         <f>[1]Prices!L$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="O26">
         <f>[1]Prices!M$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P26">
         <f>[1]Prices!N$26</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Q26">
         <f>[1]Prices!O$26</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="R26">
         <f>[1]Prices!P$26</f>
-        <v>68.341643330825832</v>
+        <v/>
       </c>
       <c r="S26">
         <f>[1]Prices!Q$26</f>
-        <v>100.32134973994673</v>
+        <v/>
       </c>
       <c r="T26">
         <f>[1]Prices!R$26</f>
-        <v>82.639006798408047</v>
+        <v/>
       </c>
       <c r="U26">
         <f>[1]Prices!S$26</f>
-        <v>67.75892127087694</v>
+        <v/>
       </c>
       <c r="V26">
         <f>[1]Prices!T$26</f>
-        <v>55.57940835560332</v>
+        <v/>
       </c>
       <c r="W26">
         <f>[1]Prices!U$26</f>
-        <v>45.789061745779293</v>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/csv/policies/reference/Ref_OBPS/formula_Ref_OBPS_MB.xlsx
+++ b/csv/policies/reference/Ref_OBPS/formula_Ref_OBPS_MB.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3624" yWindow="2148" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" calcOnSave="0"/>
 </workbook>
 </file>
 
@@ -527,12 +527,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:X26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
